--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20260106_201530.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20260106_201530.xlsx
@@ -4854,7 +4854,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20260106_201530.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20260106_201530.xlsx
@@ -7682,7 +7682,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
